--- a/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
+++ b/InputData/trans/BHNVFEAL/BAU Historical New Veh Fuel Economy After Lifetime.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\trans\BHNVFEAL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\BHNVFEAL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C13FAFD-2D0B-43B5-9E43-F1CFC13D9FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11F0C145-5EB0-4280-9DA6-AA87E9CED957}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="360" windowWidth="9800" windowHeight="10070" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="99">
   <si>
     <t>Sources:</t>
   </si>
@@ -379,9 +379,6 @@
   </si>
   <si>
     <t>energy consumption that more closely matches EIA's AEO trajectory: freight LDVs, passenger HDVs, freight HDVs, passenger ships, passenger motorbikes.</t>
-  </si>
-  <si>
-    <t>Louisiana</t>
   </si>
 </sst>
 </file>
@@ -1296,7 +1293,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1338,7 +1335,6 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="154" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="155" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="156">
     <cellStyle name="20% - Accent1 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -7789,25 +7785,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C48"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <dimension ref="A1:B48"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.40625" customWidth="1"/>
-    <col min="2" max="2" width="107.40625" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="107.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C1" s="31">
-        <v>45467</v>
-      </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -7815,58 +7805,58 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:2">
       <c r="B4" s="6" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:2">
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:2">
       <c r="B6" s="14" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:2">
       <c r="B7" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:2">
       <c r="B8" s="5">
         <v>2008</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:2">
       <c r="B9" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:2">
       <c r="B10" s="5" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:2">
       <c r="B11" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:2">
       <c r="B12" s="5"/>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:2">
       <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:2">
       <c r="B14" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:2">
       <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
@@ -8022,12 +8012,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -9016,12 +9006,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -9888,12 +9878,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -10760,14 +10750,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AF13"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
-    <col min="2" max="2" width="10.40625" customWidth="1"/>
-    <col min="3" max="3" width="10.7265625" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
+    <col min="2" max="2" width="10.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32">
+    <row r="1" spans="1:32" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -11661,12 +11651,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -12533,12 +12523,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -13519,12 +13509,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -14391,12 +14381,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -15385,12 +15375,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AE8"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:31" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -16158,11 +16148,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AK30"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.40625" customWidth="1"/>
-    <col min="2" max="2" width="16.40625" customWidth="1"/>
-    <col min="3" max="3" width="30.7265625" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.42578125" customWidth="1"/>
+    <col min="3" max="3" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:37">
@@ -18459,7 +18449,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" t="s">
@@ -18833,9 +18823,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="50.40625" customWidth="1"/>
+    <col min="1" max="1" width="50.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -18937,11 +18927,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AL31"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="42.1328125" customWidth="1"/>
-    <col min="2" max="2" width="26.40625" customWidth="1"/>
-    <col min="3" max="3" width="42.86328125" customWidth="1"/>
+    <col min="1" max="1" width="42.140625" customWidth="1"/>
+    <col min="2" max="2" width="26.42578125" customWidth="1"/>
+    <col min="3" max="3" width="42.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38">
@@ -19111,7 +19101,7 @@
         <v>5.76</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="29.5">
+    <row r="20" spans="1:4" ht="30">
       <c r="A20" s="13" t="s">
         <v>68</v>
       </c>
@@ -19129,7 +19119,7 @@
         <v>6.7042622950819668</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="29.5">
+    <row r="22" spans="1:4" ht="30">
       <c r="A22" s="13" t="s">
         <v>70</v>
       </c>
@@ -19215,11 +19205,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:BT15"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="15" max="15" width="11.40625" customWidth="1"/>
-    <col min="40" max="40" width="8.7265625" style="24"/>
+    <col min="15" max="15" width="11.42578125" customWidth="1"/>
+    <col min="40" max="40" width="8.7109375" style="24"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:72">
@@ -22664,12 +22654,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH10"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -23698,12 +23688,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
@@ -24692,12 +24682,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AH8"/>
-  <sheetFormatPr defaultRowHeight="14.75"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="31.1328125" customWidth="1"/>
+    <col min="1" max="1" width="31.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34">
+    <row r="1" spans="1:34" ht="30">
       <c r="A1" s="18" t="s">
         <v>87</v>
       </c>
